--- a/Protocolo PRISMA/Analisis 137 referencias.xlsx
+++ b/Protocolo PRISMA/Analisis 137 referencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\test\Citas seminario\PRISMA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Seminario\Protocolo PRISMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AB91CC-64B7-40DC-A991-F243D4ED5ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F2B0B0-10E9-4DA9-9AA3-9A1F8E4092AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,9 +76,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>Aporta evidencia experimental de que los pesos de atención no guardan una relación causal con la predicción del modelo. Lo tomamos como punto de partida de nuestra formulación: si la fidelidad de la atención no puede presuponerse, hay que medirla de forma explícita, que es precisamente lo que propone nuestro marco.</t>
-  </si>
-  <si>
     <t>Instability and interpretability discrepancies between CNNs and vision transformers in keratoconus detection</t>
   </si>
   <si>
@@ -88,27 +85,18 @@
     <t>Patricio</t>
   </si>
   <si>
-    <t>Cuantifica cuánto varía una explicación al reentrenar el mismo modelo con distintas semillas y contrasta ese comportamiento entre arquitecturas convolucionales y de atención. Sustenta el componente de inestabilidad estocástica de nuestra pregunta de investigación y advierte de un compromiso que debemos controlar: una explicación más estable no es necesariamente más fiel.</t>
-  </si>
-  <si>
     <t>Attribution rollout: a new way to interpret visual transformer</t>
   </si>
   <si>
     <t>10.1007/s12652-022-04354-2</t>
   </si>
   <si>
-    <t>Describe el procedimiento de propagación de la atención entre capas ponderado por atribución que empleamos para agregar las matrices por capa en una sola. Es la referencia metodológica directa de esa etapa de nuestro desarrollo.</t>
-  </si>
-  <si>
     <t>Explanation Variability in Text Classification: Humans vs. LLMs</t>
   </si>
   <si>
     <t>10.1162/COLI.a.624</t>
   </si>
   <si>
-    <t>Documenta que dos configuraciones que coinciden en la predicción pueden diferir en la explicación, y ensaya esquemas de discretización para llevar atribuciones continuas a decisiones categóricas. Ambos elementos respaldan nuestro consenso entre semillas y el criterio con el que binarizamos la matriz de atención.</t>
-  </si>
-  <si>
     <t>Explainability and Evaluation of Vision Transformers: An In-Depth Experimental Study</t>
   </si>
   <si>
@@ -118,27 +106,18 @@
     <t>Gabriel</t>
   </si>
   <si>
-    <t>Compara de forma sistemática métricas de evaluación de explicaciones sobre arquitecturas de atención y muestra que métricas que dicen medir la misma propiedad no coinciden entre sí. De ahí que en nuestra propuesta los umbrales se calibren contra modelos nulos en lugar de adoptarse de la literatura.</t>
-  </si>
-  <si>
     <t>A comprehensive analysis of perturbation methods in explainable AI feature attribution validation for neural time series classifiers</t>
   </si>
   <si>
     <t>10.1038/s41598-025-09538-2</t>
   </si>
   <si>
-    <t>Identifica limitaciones de la métrica de fidelidad más extendida cuando se aplica a datos temporales y propone criterios alternativos de evaluación. Nos obliga a justificar la métrica con la que valoramos nuestras ablaciones en vez de darla por buena.</t>
-  </si>
-  <si>
     <t>Explaining time series classifiers through meaningful perturbation and optimisation</t>
   </si>
   <si>
     <t>10.1016/j.ins.2023.119334</t>
   </si>
   <si>
-    <t>Advierte que perturbar una entrada para medir la importancia de una variable puede desplazarla fuera de la distribución de entrenamiento, con lo que se acaba midiendo la fragilidad del modelo y no la relevancia de la variable. Es el argumento por el que nuestra ablación atenúa y renormaliza en lugar de eliminar.</t>
-  </si>
-  <si>
     <t>From Black-Box to Glass-Box: Explainable Plant Disease Segmentation for Early Detection Using SegFormer</t>
   </si>
   <si>
@@ -154,9 +133,6 @@
     <t>10.4230/OASIcs.SAIA.2024.12</t>
   </si>
   <si>
-    <t>Revisa cómo los propios métodos de explicabilidad pueden ser manipulados y señala que las modalidades de series temporales y grafos apenas se han estudiado desde esa perspectiva. Lo citamos como respaldo de que las explicaciones requieren auditoría y como formulación de la brecha que abordamos.</t>
-  </si>
-  <si>
     <t>Understanding Transformer-Based Classifications of Medical Text Using a Large Language Model for the Attribution of Feature Importance: Proof-of-Concept Algorithm Development and Validation Study</t>
   </si>
   <si>
@@ -181,27 +157,18 @@
     <t>10.1016/j.egyai.2024.100368</t>
   </si>
   <si>
-    <t>Presenta una red neuronal de grafos con explicaciones causales intrínsecas y locales para predicción multivariante. Lo empleamos como término de comparación directo del resultado que perseguimos.</t>
-  </si>
-  <si>
     <t>A global model-agnostic rule-based XAI method based on Parameterized Event Primitives for time series classifiers</t>
   </si>
   <si>
     <t>10.3389/frai.2024.1381921</t>
   </si>
   <si>
-    <t>Extrae de un clasificador de series un conjunto reducido de reglas y lo evalúa a la vez por fidelidad y por tamaño, contando nodos y profundidad. Esa doble exigencia coincide con la nuestra: la estructura resultante debe ser fiel al modelo y lo bastante compacta para poder inspeccionarse.</t>
-  </si>
-  <si>
     <t>Automated Knowledge Graph Learning in Industrial Processes</t>
   </si>
   <si>
     <t>10.1016/j.procs.2025.01.303</t>
   </si>
   <si>
-    <t>Construye un grafo de conocimiento a partir de series temporales industriales combinando análisis de similitud y causalidad de Granger, y lo plantea como alternativa transparente al modelo opaco. Nos sirve de comparador del resultado y de referencia para la línea base de Granger que implementamos.</t>
-  </si>
-  <si>
     <t>Causal and spatiotemporal deep learning for dengue forecasting and extreme outbreak risk under climate variability: a framework from Vietnam</t>
   </si>
   <si>
@@ -244,18 +211,12 @@
     <t>10.3390/aerospace13070590</t>
   </si>
   <si>
-    <t>Muestra un caso en que la atención de un modelo converge por sí sola sobre una frecuencia que coincide con la predicha por la teoría aerodinámica. Es el único ejemplo que hemos encontrado en que la atención recupera un mecanismo verificable de forma independiente, y nos permite argumentar por qué un conjunto de variables muy colineales, sin firma propia, plantea un problema más difícil.</t>
-  </si>
-  <si>
     <t>An end-to-end explainability framework for spatio-temporal predictive modeling</t>
   </si>
   <si>
     <t>10.1007/s10994-024-06733-6</t>
   </si>
   <si>
-    <t>Desarrolla explicaciones para modelos espacio-temporales sobre redes de sensores, desglosadas por variable, por instante y por localización. Es la estructura de datos más próxima a la nuestra y el comparador externo frente al que contrastamos un método intrínseco.</t>
-  </si>
-  <si>
     <t>Generative Imputation with Multi-level Causal Consistency for Variable Subset Forecasting</t>
   </si>
   <si>
@@ -263,13 +224,52 @@
   </si>
   <si>
     <t>Aborda la imputación cuando faltan variables completas imponiendo consistencia causal, con el fin de separar la dependencia genuina de la correlación espuria. Es el análogo formal de la tarea de enmascaramiento con la que entrenamos nuestro modelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documenta que dos configuraciones que coinciden en la predicción pueden diferir en la explicación, y ensaya esquemas de discretización para llevar atribuciones continuas a decisiones categóricas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describe el procedimiento de propagación de la atención entre capas ponderado por atribución que empleamos para agregar las matrices por capa en una sola. </t>
+  </si>
+  <si>
+    <t>Cuantifica cuánto varía una explicación al reentrenar el mismo modelo con distintas semillas y contrasta ese comportamiento entre arquitecturas convolucionales y de atención.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aporta evidencia experimental de que los pesos de atención no guardan una relación causal con la predicción del modelo. </t>
+  </si>
+  <si>
+    <t>Compara de forma sistemática métricas de evaluación de explicaciones sobre arquitecturas de atención y muestra que métricas que dicen medir la misma propiedad no coinciden entre sí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifica limitaciones de la métrica de fidelidad más extendida cuando se aplica a datos temporales y propone criterios alternativos de evaluación. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advierte que perturbar una entrada para medir la importancia de una variable puede desplazarla fuera de la distribución de entrenamiento, con lo que se acaba midiendo la fragilidad del modelo y no la relevancia de la variable. </t>
+  </si>
+  <si>
+    <t>Revisa cómo los propios métodos de explicabilidad pueden ser manipulados y señala que las modalidades de series temporales y grafos apenas se han estudiado desde esa perspectiva.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presenta una red neuronal de grafos con explicaciones causales intrínsecas y locales para predicción multivariante. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrae de un clasificador de series un conjunto reducido de reglas y lo evalúa a la vez por fidelidad y por tamaño, contando nodos y profundidad. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construye un grafo de conocimiento a partir de series temporales industriales combinando análisis de similitud y causalidad de Granger, y lo plantea como alternativa transparente al modelo opaco. </t>
+  </si>
+  <si>
+    <t>Muestra un caso en que la atención de un modelo converge por sí sola sobre una frecuencia que coincide con la predicha por la teoría aerodinámica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrolla explicaciones para modelos espacio-temporales sobre redes de sensores, desglosadas por variable, por instante y por localización. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +282,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -309,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -320,14 +327,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -353,6 +360,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -376,12 +392,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -396,11 +406,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{259E14A1-6754-4E7D-B185-AF8BE5C44137}" name="Table1" displayName="Table1" ref="A1:M22" totalsRowShown="0" headerRowDxfId="9" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{259E14A1-6754-4E7D-B185-AF8BE5C44137}" name="Table1" displayName="Table1" ref="A1:M22" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:M22" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{7F1AFC88-6609-4386-B042-B8489D836FAF}" name="N PDF"/>
-    <tableColumn id="2" xr3:uid="{0298C1C0-ACB5-44D5-BBE1-45A0F73B19C4}" name="Título" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0298C1C0-ACB5-44D5-BBE1-45A0F73B19C4}" name="Título" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{D5F6B8FC-5D10-4F38-A64E-89126E1FA609}" name="DOI"/>
     <tableColumn id="4" xr3:uid="{017F719E-F67A-4AD8-88BC-87DA4067DA7E}" name="Propuesto por"/>
     <tableColumn id="5" xr3:uid="{F2B374C9-16D8-4C00-9948-F5EF30D73B15}" name="Resumen" dataDxfId="8"/>
@@ -410,8 +420,8 @@
     <tableColumn id="9" xr3:uid="{766CA4CE-F243-4AEB-8E00-36C3DABFDBA1}" name="Marco Teórico" dataDxfId="4"/>
     <tableColumn id="10" xr3:uid="{8384043E-C45E-4BFB-9DA2-21288825D0CA}" name="Plan de trabajo" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{7763FC13-9AD6-4D31-9C3A-4F4110D70EC4}" name="Propuesta" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{9D4D2798-7F98-4FC4-B01D-EDB4A1503BC1}" name="Conclusiones" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{5853DE1E-9E42-448F-822A-3CC3A11DF35A}" name="Motivo de inclusión" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{9D4D2798-7F98-4FC4-B01D-EDB4A1503BC1}" name="Conclusiones" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{5853DE1E-9E42-448F-822A-3CC3A11DF35A}" name="Motivo de inclusión" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -720,7 +730,7 @@
     <col min="13" max="13" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>119</v>
       </c>
@@ -789,21 +799,21 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -820,21 +830,21 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>107</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -849,18 +859,18 @@
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>116</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -880,21 +890,21 @@
         <v>16</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -911,21 +921,21 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>117</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -940,7 +950,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -948,10 +958,10 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -969,21 +979,21 @@
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="2" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>120</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>38</v>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
@@ -1000,21 +1010,21 @@
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
@@ -1031,7 +1041,7 @@
         <v>16</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1039,13 +1049,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1062,7 +1072,7 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1070,10 +1080,10 @@
         <v>103</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1095,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1103,13 +1113,13 @@
         <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1124,21 +1134,21 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1155,21 +1165,21 @@
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1184,21 +1194,21 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="2" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>108</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>59</v>
+      <c r="B16" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
@@ -1215,21 +1225,21 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>105</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>62</v>
+      <c r="B17" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
@@ -1246,7 +1256,7 @@
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1254,13 +1264,13 @@
         <v>121</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1277,7 +1287,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1285,13 +1295,13 @@
         <v>131</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1308,21 +1318,21 @@
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1339,18 +1349,18 @@
         <v>16</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>101</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -1370,7 +1380,7 @@
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1378,13 +1388,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1401,7 +1411,7 @@
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
